--- a/resources/tool_kii_fsl_service_provider_iphra_v2.xlsx
+++ b/resources/tool_kii_fsl_service_provider_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05261A81-D617-4911-9C47-6901F7E33E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB47488-64E5-45B3-8486-6744BEA8563F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="159">
   <si>
     <t>type</t>
   </si>
@@ -517,12 +517,6 @@
   </si>
   <si>
     <t>groups_limited_access_barriers_other</t>
-  </si>
-  <si>
-    <t>22003, 37001</t>
-  </si>
-  <si>
-    <t>23005, 38001</t>
   </si>
 </sst>
 </file>
@@ -575,7 +569,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -600,6 +594,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -613,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -631,6 +631,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1305,8 +1306,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>32103</v>
+      <c r="A16" s="11">
+        <v>12306</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>77</v>
@@ -1319,8 +1320,8 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>32104</v>
+      <c r="A17" s="11">
+        <v>12306</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>19</v>
@@ -1333,8 +1334,8 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>23004</v>
+      <c r="A18" s="11">
+        <v>11404</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>116</v>
@@ -1347,8 +1348,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>23004</v>
+      <c r="A19" s="11">
+        <v>11404</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>120</v>
@@ -1362,8 +1363,8 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>23004</v>
+      <c r="A20" s="11">
+        <v>11404</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>19</v>
@@ -1377,8 +1378,8 @@
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>159</v>
+      <c r="A21" s="11">
+        <v>11303</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>19</v>
@@ -1391,8 +1392,8 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>160</v>
+      <c r="A22" s="11">
+        <v>12901</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>19</v>
@@ -1405,8 +1406,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22004</v>
+      <c r="A23" s="11">
+        <v>11304</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>137</v>
@@ -1419,8 +1420,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>22004</v>
+      <c r="A24" s="11">
+        <v>11304</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>19</v>
@@ -1433,8 +1434,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>22004</v>
+      <c r="A25" s="11">
+        <v>11304</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>19</v>
@@ -1447,8 +1448,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>23006</v>
+      <c r="A26" s="11">
+        <v>11406</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>116</v>
@@ -1461,8 +1462,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>23006</v>
+      <c r="A27" s="11">
+        <v>11406</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>19</v>
@@ -1475,8 +1476,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>23006</v>
+      <c r="A28" s="11">
+        <v>11406</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>137</v>
@@ -1489,8 +1490,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>23006</v>
+      <c r="A29" s="11">
+        <v>11406</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>19</v>
@@ -1503,8 +1504,8 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>23006</v>
+      <c r="A30" s="11">
+        <v>11406</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>19</v>
@@ -1517,8 +1518,8 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>32103</v>
+      <c r="A31" s="11">
+        <v>12305</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>137</v>
@@ -1531,8 +1532,8 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>32103</v>
+      <c r="A32" s="11">
+        <v>12305</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>19</v>
@@ -1545,8 +1546,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32103</v>
+      <c r="A33" s="11">
+        <v>12305</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>19</v>
@@ -1614,11 +1615,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="C7">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C21:C22">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2084,8 +2085,8 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>32103</v>
+      <c r="A28" s="11">
+        <v>12306</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
@@ -2098,8 +2099,8 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>32103</v>
+      <c r="A29" s="11">
+        <v>12306</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>68</v>
@@ -2112,8 +2113,8 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>32103</v>
+      <c r="A30" s="11">
+        <v>12306</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>68</v>
@@ -2126,8 +2127,8 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>32103</v>
+      <c r="A31" s="11">
+        <v>12306</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>68</v>
@@ -2140,8 +2141,8 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>32103</v>
+      <c r="A32" s="11">
+        <v>12306</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>68</v>
@@ -2154,8 +2155,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32103</v>
+      <c r="A33" s="11">
+        <v>12306</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>68</v>
@@ -2168,8 +2169,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>32103</v>
+      <c r="A34" s="11">
+        <v>12306</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>68</v>
@@ -2182,8 +2183,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>32103</v>
+      <c r="A35" s="11">
+        <v>12306</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>68</v>
@@ -2196,8 +2197,8 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>32103</v>
+      <c r="A36" s="11">
+        <v>12306</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>68</v>
@@ -2210,8 +2211,8 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>23004</v>
+      <c r="A37" s="11">
+        <v>11404</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>121</v>
@@ -2224,8 +2225,8 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>23004</v>
+      <c r="A38" s="11">
+        <v>11404</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>121</v>
@@ -2238,8 +2239,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>23004</v>
+      <c r="A39" s="11">
+        <v>11404</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>121</v>
@@ -2252,8 +2253,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>23004</v>
+      <c r="A40" s="11">
+        <v>11404</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>121</v>
@@ -2266,8 +2267,8 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>23004</v>
+      <c r="A41" s="11">
+        <v>11404</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>121</v>
@@ -2283,14 +2284,14 @@
   <conditionalFormatting sqref="C4:C6">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C27">
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C7:C10">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:C27">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2332,12 +2333,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2582,20 +2585,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
+    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2620,12 +2624,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
-    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/resources/tool_kii_fsl_service_provider_iphra_v2.xlsx
+++ b/resources/tool_kii_fsl_service_provider_iphra_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB47488-64E5-45B3-8486-6744BEA8563F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FD0BDB-EC36-4686-9363-800B51E7106D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
+    <workbookView xWindow="4455" yWindow="0" windowWidth="14535" windowHeight="15480" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="170">
   <si>
     <t>type</t>
   </si>
@@ -517,6 +517,39 @@
   </si>
   <si>
     <t>groups_limited_access_barriers_other</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
   </si>
 </sst>
 </file>
@@ -636,7 +669,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1616,10 +1659,10 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:C22">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1627,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5703125" style="2" customWidth="1"/>
@@ -1885,16 +1928,16 @@
         <v>10000</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>95</v>
+        <v>159</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1902,16 +1945,16 @@
         <v>10000</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>98</v>
+        <v>159</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1919,16 +1962,16 @@
         <v>10000</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>99</v>
+        <v>159</v>
+      </c>
+      <c r="C18" s="8">
+        <v>3</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1936,16 +1979,16 @@
         <v>10000</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>101</v>
+        <v>159</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1953,16 +1996,16 @@
         <v>10000</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>102</v>
+        <v>159</v>
+      </c>
+      <c r="C20" s="8">
+        <v>5</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1970,10 +2013,10 @@
         <v>10000</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>96</v>
@@ -1987,10 +2030,10 @@
         <v>10000</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>96</v>
@@ -2004,10 +2047,10 @@
         <v>10000</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>96</v>
@@ -2021,10 +2064,10 @@
         <v>10000</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>96</v>
@@ -2038,10 +2081,10 @@
         <v>10000</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>96</v>
@@ -2055,10 +2098,10 @@
         <v>10000</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>96</v>
@@ -2072,10 +2115,10 @@
         <v>10000</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>96</v>
@@ -2084,74 +2127,89 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
-        <v>12306</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <v>12306</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>12306</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>12306</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
-        <v>12306</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>63</v>
+    <row r="28" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2162,10 +2220,10 @@
         <v>68</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>64</v>
+        <v>70</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2176,10 +2234,10 @@
         <v>68</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2190,10 +2248,10 @@
         <v>68</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2204,94 +2262,167 @@
         <v>68</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>11404</v>
+        <v>12306</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>122</v>
+        <v>74</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>11404</v>
+        <v>12306</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>123</v>
+        <v>75</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>11404</v>
+        <v>12306</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>124</v>
+        <v>73</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>11404</v>
+        <v>12306</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>125</v>
+        <v>76</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>11404</v>
+        <v>12306</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>11404</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="11">
+        <v>11404</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>11404</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>11404</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>11404</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C6">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C10">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="C21:C32">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C27">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  <conditionalFormatting sqref="C16:C20">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2333,14 +2464,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2585,21 +2714,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
-    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2624,9 +2752,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
+    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>